--- a/storage/app/templates/plantilla_mantenimiento_equipo.xlsx
+++ b/storage/app/templates/plantilla_mantenimiento_equipo.xlsx
@@ -1,183 +1,168 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="500" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="REPORTE DE MANTENIMIENTO" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="REPORTE DE MANTENIMIENTO" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="32">
   <si>
     <t xml:space="preserve">FORMATO DE REPORTE DE MANTENIMIENTO DE EQUIPOS DE COMPUTO </t>
   </si>
   <si>
-    <t xml:space="preserve">Código: PTSI-FO-04</t>
+    <t>Código: PTSI-FO-04</t>
   </si>
   <si>
     <t xml:space="preserve"> Fecha de Aprobación:                      02/01/2024</t>
   </si>
   <si>
-    <t xml:space="preserve">PROCESO: TECNOLOGIA Y SISTEMAS DE INFORMACION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Versión: 01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOMBRE DE LA EMPRESA:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOMBRE EQUIPO:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARCA:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MODELO:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERIE:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBICACION:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FECHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PANTALLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TECLADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOUSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIDAD CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANTENIMIENTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DESCRIPCION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REPUESTOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANTIDAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COSTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOMBRE DE REPUESTOS</t>
+    <t>PROCESO: TECNOLOGIA Y SISTEMAS DE INFORMACION</t>
+  </si>
+  <si>
+    <t>Versión: 01</t>
+  </si>
+  <si>
+    <t>NOMBRE DE LA EMPRESA:</t>
+  </si>
+  <si>
+    <t>NOMBRE EQUIPO:</t>
+  </si>
+  <si>
+    <t>MARCA:</t>
+  </si>
+  <si>
+    <t>MODELO:</t>
+  </si>
+  <si>
+    <t>SERIE:</t>
+  </si>
+  <si>
+    <t>UBICACION:</t>
+  </si>
+  <si>
+    <t>FECHA</t>
+  </si>
+  <si>
+    <t>CPU</t>
+  </si>
+  <si>
+    <t>PANTALLA</t>
+  </si>
+  <si>
+    <t>TECLADO</t>
+  </si>
+  <si>
+    <t>MOUSE</t>
+  </si>
+  <si>
+    <t>UNIDAD CD</t>
+  </si>
+  <si>
+    <t>MANTENIMIENTO</t>
+  </si>
+  <si>
+    <t>DESCRIPCION</t>
+  </si>
+  <si>
+    <t>REPUESTOS</t>
+  </si>
+  <si>
+    <t>CANTIDAD</t>
+  </si>
+  <si>
+    <t>COSTO</t>
+  </si>
+  <si>
+    <t>NOMBRE DE REPUESTOS</t>
   </si>
   <si>
     <t xml:space="preserve">FIRMA PERSONAL A CARGO </t>
   </si>
   <si>
-    <t xml:space="preserve">FIRMA SISTEMAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AAAA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREVENTIVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORRECTIVO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO</t>
+    <t>FIRMA SISTEMAS</t>
+  </si>
+  <si>
+    <t>AAAA</t>
+  </si>
+  <si>
+    <t>MM</t>
+  </si>
+  <si>
+    <t>DD</t>
+  </si>
+  <si>
+    <t>PREVENTIVO</t>
+  </si>
+  <si>
+    <t>CORRECTIVO</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>NO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -189,163 +174,143 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="17">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="true">
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="true">
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>123840</xdr:colOff>
+      <xdr:colOff>123825</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>19080</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>228240</xdr:colOff>
+      <xdr:colOff>228600</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>27720</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="image2.jpg"/>
-        <xdr:cNvPicPr/>
+        <xdr:cNvPr id="1" name="image2.jpg" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="225360" y="95400"/>
-          <a:ext cx="1618200" cy="827640"/>
+        <a:xfrm rot="0">
+          <a:ext cx="1524000" cy="781050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -354,14 +319,14 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -396,157 +361,239 @@
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:ea typeface="Calibri" pitchFamily="0" charset="1"/>
-        <a:cs typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AL1000"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr customHeight="true" defaultRowHeight="15" defaultColWidth="14.453125" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="1.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="2" style="1" width="4.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="7.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="4.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="15" style="1" width="4.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="6.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="25" style="1" width="4.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="5.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="33" style="1" width="4.73"/>
+    <col min="1" max="1" width="1.27" customWidth="true" style="1"/>
+    <col min="2" max="2" width="4.73" customWidth="true" style="1"/>
+    <col min="3" max="3" width="4.73" customWidth="true" style="1"/>
+    <col min="4" max="4" width="4.73" customWidth="true" style="1"/>
+    <col min="5" max="5" width="4.73" customWidth="true" style="1"/>
+    <col min="6" max="6" width="4.73" customWidth="true" style="1"/>
+    <col min="7" max="7" width="4.73" customWidth="true" style="1"/>
+    <col min="8" max="8" width="4.73" customWidth="true" style="1"/>
+    <col min="9" max="9" width="4.73" customWidth="true" style="1"/>
+    <col min="10" max="10" width="4.73" customWidth="true" style="1"/>
+    <col min="11" max="11" width="4.73" customWidth="true" style="1"/>
+    <col min="12" max="12" width="7.82" customWidth="true" style="1"/>
+    <col min="13" max="13" width="4.73" customWidth="true" style="1"/>
+    <col min="14" max="14" width="8" customWidth="true" style="1"/>
+    <col min="15" max="15" width="4.73" customWidth="true" style="1"/>
+    <col min="16" max="16" width="4.73" customWidth="true" style="1"/>
+    <col min="17" max="17" width="4.73" customWidth="true" style="1"/>
+    <col min="18" max="18" width="4.73" customWidth="true" style="1"/>
+    <col min="19" max="19" width="4.73" customWidth="true" style="1"/>
+    <col min="20" max="20" width="4.73" customWidth="true" style="1"/>
+    <col min="21" max="21" width="4.73" customWidth="true" style="1"/>
+    <col min="22" max="22" width="4.73" customWidth="true" style="1"/>
+    <col min="23" max="23" width="4.73" customWidth="true" style="1"/>
+    <col min="24" max="24" width="6.73" customWidth="true" style="1"/>
+    <col min="25" max="25" width="4.73" customWidth="true" style="1"/>
+    <col min="26" max="26" width="4.73" customWidth="true" style="1"/>
+    <col min="27" max="27" width="4.73" customWidth="true" style="1"/>
+    <col min="28" max="28" width="4.73" customWidth="true" style="1"/>
+    <col min="29" max="29" width="4.73" customWidth="true" style="1"/>
+    <col min="30" max="30" width="4.73" customWidth="true" style="1"/>
+    <col min="31" max="31" width="4.73" customWidth="true" style="1"/>
+    <col min="32" max="32" width="5.09" customWidth="true" style="1"/>
+    <col min="33" max="33" width="4.73" customWidth="true" style="1"/>
+    <col min="34" max="34" width="4.73" customWidth="true" style="1"/>
+    <col min="35" max="35" width="4.73" customWidth="true" style="1"/>
+    <col min="36" max="36" width="4.73" customWidth="true" style="1"/>
+    <col min="37" max="37" width="4.73" customWidth="true" style="1"/>
+    <col min="38" max="38" width="4.73" customWidth="true" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:38" customHeight="1" ht="6"/>
+    <row r="2" spans="1:38" customHeight="1" ht="15">
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -589,7 +636,7 @@
       <c r="AK2" s="4"/>
       <c r="AL2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:38" customHeight="1" ht="15">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -630,7 +677,7 @@
       <c r="AK3" s="5"/>
       <c r="AL3" s="5"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:38" customHeight="1" ht="15">
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -669,7 +716,7 @@
       <c r="AK4" s="5"/>
       <c r="AL4" s="5"/>
     </row>
-    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:38" customHeight="1" ht="19.5">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -712,7 +759,7 @@
       <c r="AK5" s="4"/>
       <c r="AL5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:38" customHeight="1" ht="19.5">
       <c r="B6" s="6" t="s">
         <v>5</v>
       </c>
@@ -753,7 +800,7 @@
       <c r="AK6" s="6"/>
       <c r="AL6" s="6"/>
     </row>
-    <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:38" customHeight="1" ht="19.5">
       <c r="B7" s="6" t="s">
         <v>6</v>
       </c>
@@ -800,7 +847,7 @@
       <c r="AK7" s="6"/>
       <c r="AL7" s="6"/>
     </row>
-    <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:38" customHeight="1" ht="18.75">
       <c r="B8" s="6" t="s">
         <v>10</v>
       </c>
@@ -841,7 +888,7 @@
       <c r="AK8" s="6"/>
       <c r="AL8" s="6"/>
     </row>
-    <row r="9" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:38" customHeight="1" ht="27">
       <c r="B9" s="7" t="s">
         <v>11</v>
       </c>
@@ -908,7 +955,7 @@
       <c r="AK9" s="11"/>
       <c r="AL9" s="11"/>
     </row>
-    <row r="10" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:38" customHeight="1" ht="39">
       <c r="B10" s="7" t="s">
         <v>25</v>
       </c>
@@ -961,7 +1008,7 @@
       <c r="AK10" s="11"/>
       <c r="AL10" s="11"/>
     </row>
-    <row r="11" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:38" customHeight="1" ht="78.75">
       <c r="A11" s="12"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -1001,7 +1048,7 @@
       <c r="AK11" s="13"/>
       <c r="AL11" s="13"/>
     </row>
-    <row r="12" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:38" customHeight="1" ht="79.5">
       <c r="A12" s="12"/>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -1041,7 +1088,7 @@
       <c r="AK12" s="13"/>
       <c r="AL12" s="13"/>
     </row>
-    <row r="13" customFormat="false" ht="80.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:38" customHeight="1" ht="80.25">
       <c r="A13" s="12"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -1081,7 +1128,7 @@
       <c r="AK13" s="13"/>
       <c r="AL13" s="13"/>
     </row>
-    <row r="14" customFormat="false" ht="81" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:38" customHeight="1" ht="81">
       <c r="A14" s="12"/>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -1121,7 +1168,7 @@
       <c r="AK14" s="13"/>
       <c r="AL14" s="13"/>
     </row>
-    <row r="15" customFormat="false" ht="85.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:38" customHeight="1" ht="85.5">
       <c r="A15" s="12"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -1161,7 +1208,7 @@
       <c r="AK15" s="13"/>
       <c r="AL15" s="13"/>
     </row>
-    <row r="16" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:38" customHeight="1" ht="84.75">
       <c r="A16" s="12"/>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -1201,7 +1248,7 @@
       <c r="AK16" s="13"/>
       <c r="AL16" s="13"/>
     </row>
-    <row r="17" customFormat="false" ht="86.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:38" customHeight="1" ht="86.25">
       <c r="A17" s="12"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -1241,7 +1288,7 @@
       <c r="AK17" s="13"/>
       <c r="AL17" s="13"/>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:38" customHeight="1" ht="14.25">
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
       <c r="D18" s="15"/>
@@ -1274,7 +1321,7 @@
       <c r="AK18" s="16"/>
       <c r="AL18" s="16"/>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:38" customHeight="1" ht="14.25">
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="15"/>
@@ -1307,7 +1354,7 @@
       <c r="AK19" s="16"/>
       <c r="AL19" s="16"/>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:38" customHeight="1" ht="14.25">
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="15"/>
@@ -1340,7 +1387,7 @@
       <c r="AK20" s="16"/>
       <c r="AL20" s="16"/>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:38" customHeight="1" ht="15.75">
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
       <c r="D21" s="15"/>
@@ -1373,7 +1420,7 @@
       <c r="AK21" s="16"/>
       <c r="AL21" s="16"/>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:38" customHeight="1" ht="15.75">
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="15"/>
@@ -1406,7 +1453,7 @@
       <c r="AK22" s="16"/>
       <c r="AL22" s="16"/>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:38" customHeight="1" ht="15.75">
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
       <c r="D23" s="15"/>
@@ -1439,7 +1486,7 @@
       <c r="AK23" s="16"/>
       <c r="AL23" s="16"/>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:38" customHeight="1" ht="15.75">
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
       <c r="D24" s="15"/>
@@ -1472,7 +1519,7 @@
       <c r="AK24" s="16"/>
       <c r="AL24" s="16"/>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:38" customHeight="1" ht="15.75">
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
       <c r="D25" s="15"/>
@@ -1505,7 +1552,7 @@
       <c r="AK25" s="16"/>
       <c r="AL25" s="16"/>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:38" customHeight="1" ht="15.75">
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
       <c r="D26" s="15"/>
@@ -1538,7 +1585,7 @@
       <c r="AK26" s="16"/>
       <c r="AL26" s="16"/>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:38" customHeight="1" ht="15.75">
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
       <c r="D27" s="15"/>
@@ -1571,7 +1618,7 @@
       <c r="AK27" s="16"/>
       <c r="AL27" s="16"/>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:38" customHeight="1" ht="15.75">
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
       <c r="D28" s="15"/>
@@ -1604,7 +1651,7 @@
       <c r="AK28" s="16"/>
       <c r="AL28" s="16"/>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:38" customHeight="1" ht="15.75">
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
       <c r="D29" s="15"/>
@@ -1637,7 +1684,7 @@
       <c r="AK29" s="16"/>
       <c r="AL29" s="16"/>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:38" customHeight="1" ht="15.75">
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
       <c r="D30" s="15"/>
@@ -1670,7 +1717,7 @@
       <c r="AK30" s="16"/>
       <c r="AL30" s="16"/>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:38" customHeight="1" ht="15.75">
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
       <c r="D31" s="15"/>
@@ -1703,7 +1750,7 @@
       <c r="AK31" s="16"/>
       <c r="AL31" s="16"/>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:38" customHeight="1" ht="15.75">
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
       <c r="D32" s="15"/>
@@ -1736,976 +1783,976 @@
       <c r="AK32" s="16"/>
       <c r="AL32" s="16"/>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="178" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="179" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="180" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="181" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="185" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="186" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="187" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="188" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="189" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="190" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="191" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="192" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="193" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="194" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="195" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="196" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="197" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="198" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="199" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="200" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="201" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="202" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="203" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="204" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="205" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="206" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="207" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="208" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="209" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="210" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="211" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="212" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="215" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="216" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="217" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="218" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="219" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="220" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="221" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="222" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="223" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="224" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="225" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="226" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="227" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="228" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="229" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="230" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="231" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="232" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="233" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="236" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="237" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="238" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="239" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="240" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="241" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="242" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="243" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="244" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="245" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="246" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="247" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="248" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="249" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="250" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="251" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="252" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="253" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="254" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="255" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="256" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="257" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="258" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="259" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="260" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="261" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="262" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="263" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="264" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="265" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="266" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="267" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="268" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="269" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="270" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="271" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="272" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="273" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="274" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="275" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="276" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="277" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="278" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="279" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="282" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="283" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="284" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="285" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="286" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="287" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="288" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="289" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="290" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="291" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="292" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="293" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="294" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="295" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="296" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="297" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="298" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="299" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="300" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="301" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="302" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="303" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="304" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="305" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="306" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="307" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="308" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="309" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="310" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="311" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="312" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="313" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="314" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="315" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="316" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="317" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="318" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="319" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="320" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="321" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="322" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="323" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="324" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="325" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="326" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="327" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="328" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="329" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="330" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="331" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="332" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="333" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="334" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="335" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="336" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="337" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="338" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="339" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="340" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="341" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="342" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="343" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="344" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="345" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="346" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="347" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="348" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="349" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="350" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="351" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="352" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="353" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="354" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="355" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="356" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="357" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="358" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="359" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="360" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="361" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="362" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="363" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="364" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="365" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="366" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="367" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="368" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="369" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="370" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="371" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="372" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="373" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="374" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="375" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="376" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="377" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="378" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="379" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="380" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="381" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="382" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="383" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="384" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="385" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="386" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="387" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="388" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="389" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="390" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="391" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="392" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="393" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="394" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="395" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="396" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="397" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="398" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="399" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="400" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="401" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="402" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="403" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="404" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="405" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="406" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="407" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="408" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="409" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="410" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="411" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="412" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="413" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="414" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="415" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="416" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="417" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="418" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="419" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="420" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="421" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="422" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="423" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="424" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="425" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="426" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="427" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="428" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="429" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="430" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="431" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="432" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="433" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="434" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="435" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="436" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="437" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="438" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="439" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="440" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="441" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="442" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="443" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="444" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="445" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="446" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="447" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="448" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="449" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="450" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="451" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="452" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="453" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="454" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="455" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="456" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="457" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="458" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="459" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="460" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="461" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="462" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="463" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="464" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="465" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="466" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="467" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="468" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="469" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="470" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="471" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="472" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="473" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="474" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="475" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="476" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="477" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="478" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="479" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="480" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="481" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="482" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="483" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="484" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="485" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="486" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="487" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="488" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="489" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="490" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="491" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="492" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="493" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="494" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="495" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="496" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="497" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="498" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="499" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="500" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="501" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="502" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="503" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="504" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="505" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="506" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="507" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="508" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="509" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="510" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="511" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="512" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="513" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="514" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="515" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="516" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="517" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="518" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="519" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="520" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="521" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="522" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="523" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="524" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="525" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="526" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="527" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="528" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="529" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="530" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="531" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="532" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="533" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="534" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="535" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="536" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="537" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="538" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="539" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="540" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="541" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="542" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="543" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="544" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="545" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="546" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="547" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="548" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="549" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="550" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="551" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="552" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="553" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="554" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="555" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="556" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="557" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="558" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="559" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="560" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="561" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="562" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="563" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="564" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="565" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="566" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="567" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="568" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="569" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="570" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="571" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="572" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="573" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="574" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="575" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="576" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="577" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="578" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="579" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="580" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="581" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="582" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="583" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="584" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="585" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="586" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="587" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="588" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="589" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="590" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="591" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="592" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="593" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="594" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="595" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="596" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="597" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="598" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="599" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="600" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="601" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="602" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="603" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="604" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="605" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="606" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="607" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="608" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="609" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="610" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="611" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="612" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="613" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="614" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="615" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="616" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="617" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="618" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="619" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="620" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="621" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="622" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="623" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="624" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="625" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="626" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="627" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="628" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="629" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="630" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="631" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="632" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="633" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="634" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="635" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="636" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="637" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="638" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="639" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="640" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="641" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="642" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="643" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="644" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="645" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="646" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="647" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="648" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="649" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="650" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="651" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="652" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="653" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="654" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="655" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="656" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="657" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="658" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="659" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="660" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="661" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="662" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="663" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="664" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="665" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="666" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="667" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="668" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="669" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="670" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="671" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="672" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="673" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="674" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="675" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="676" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="677" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="678" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="679" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="680" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="681" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="682" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="683" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="684" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="685" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="686" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="687" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="688" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="689" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="690" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="691" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="692" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="693" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="694" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="695" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="696" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="697" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="698" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="699" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="700" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="701" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="702" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="703" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="704" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="705" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="706" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="707" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="708" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="709" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="710" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="711" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="712" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="713" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="714" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="715" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="716" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="717" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="718" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="719" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="720" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="721" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="722" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="723" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="724" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="725" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="726" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="727" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="728" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="729" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="730" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="731" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="732" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="733" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="734" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="735" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="736" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="737" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="738" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="739" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="740" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="741" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="742" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="743" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="744" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="745" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="746" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="747" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="748" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="749" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="750" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="751" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="752" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="753" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="754" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="755" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="756" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="757" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="758" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="759" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="760" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="761" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="762" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="763" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="764" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="765" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="766" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="767" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="768" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="769" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="770" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="771" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="772" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="773" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="774" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="775" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="776" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="777" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="778" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="779" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="780" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="781" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="782" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="783" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="784" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="785" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="786" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="787" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="788" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="789" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="790" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="791" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="792" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="793" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="794" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="795" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="796" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="797" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="798" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="799" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="800" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="801" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="802" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="803" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="804" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="805" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="806" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="807" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="808" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="809" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="810" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="811" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="812" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="813" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="814" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="815" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="816" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="817" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="818" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="819" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="820" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="821" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="822" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="823" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="824" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="825" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="826" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="827" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="828" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="829" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="830" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="831" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="832" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="833" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="834" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="835" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="836" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="837" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="838" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="839" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="840" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="841" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="842" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="843" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="844" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="845" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="846" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="847" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="848" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="849" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="850" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="851" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="852" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="853" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="854" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="855" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="856" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="857" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="858" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="859" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="860" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="861" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="862" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="863" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="864" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="865" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="866" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="867" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="868" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="869" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="870" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="871" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="872" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="873" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="874" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="875" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="876" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="877" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="878" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="879" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="880" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="881" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="882" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="883" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="884" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="885" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="886" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="887" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="888" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="889" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="890" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="891" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="892" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="893" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="894" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="895" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="896" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="897" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="898" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="899" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="900" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="901" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="902" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="903" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="904" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="905" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="906" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="907" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="908" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="909" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="910" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="911" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="912" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="913" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="914" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="915" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="916" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="917" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="918" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="919" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="920" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="921" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="922" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="923" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="924" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="925" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="926" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="927" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="928" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="929" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="930" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="931" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="932" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="933" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="934" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="935" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="936" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="937" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="938" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="939" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="940" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="941" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="942" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="943" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="944" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="945" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="946" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="947" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="948" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="949" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="950" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="951" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="952" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="953" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="954" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="955" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="956" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="957" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="958" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="959" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="960" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="961" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="962" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="963" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="964" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="965" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="966" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="967" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="968" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="969" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="970" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="971" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="972" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="973" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="974" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="975" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="976" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="977" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="978" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="979" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="980" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="981" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="982" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="983" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="984" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="985" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="986" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="987" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="988" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="989" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="990" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="991" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="992" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="993" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="994" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="995" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="996" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="997" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="998" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="999" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1000" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="33" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="34" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="35" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="36" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="37" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="38" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="39" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="40" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="41" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="42" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="43" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="44" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="45" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="46" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="47" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="48" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="49" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="50" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="51" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="52" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="53" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="54" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="55" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="56" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="57" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="58" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="59" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="60" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="61" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="62" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="63" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="64" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="65" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="66" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="67" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="68" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="69" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="70" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="71" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="72" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="73" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="74" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="75" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="76" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="77" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="78" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="79" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="80" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="81" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="82" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="83" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="84" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="85" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="86" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="87" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="88" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="89" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="90" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="91" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="92" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="93" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="94" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="95" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="96" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="97" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="98" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="99" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="100" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="101" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="102" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="103" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="104" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="105" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="106" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="107" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="108" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="109" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="110" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="111" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="112" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="113" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="114" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="115" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="116" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="117" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="118" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="119" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="120" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="121" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="122" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="123" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="124" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="125" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="126" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="127" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="128" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="129" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="130" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="131" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="132" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="133" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="134" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="135" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="136" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="137" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="138" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="139" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="140" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="141" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="142" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="143" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="144" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="145" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="146" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="147" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="148" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="149" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="150" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="151" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="152" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="153" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="154" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="155" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="156" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="157" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="158" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="159" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="160" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="161" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="162" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="163" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="164" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="165" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="166" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="167" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="168" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="169" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="170" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="171" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="172" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="173" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="174" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="175" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="176" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="177" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="178" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="179" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="180" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="181" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="182" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="183" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="184" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="185" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="186" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="187" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="188" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="189" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="190" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="191" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="192" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="193" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="194" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="195" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="196" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="197" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="198" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="199" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="200" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="201" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="202" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="203" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="204" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="205" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="206" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="207" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="208" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="209" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="210" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="211" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="212" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="213" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="214" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="215" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="216" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="217" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="218" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="219" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="220" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="221" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="222" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="223" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="224" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="225" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="226" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="227" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="228" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="229" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="230" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="231" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="232" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="233" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="234" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="235" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="236" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="237" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="238" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="239" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="240" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="241" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="242" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="243" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="244" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="245" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="246" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="247" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="248" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="249" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="250" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="251" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="252" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="253" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="254" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="255" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="256" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="257" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="258" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="259" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="260" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="261" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="262" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="263" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="264" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="265" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="266" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="267" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="268" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="269" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="270" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="271" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="272" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="273" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="274" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="275" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="276" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="277" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="278" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="279" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="280" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="281" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="282" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="283" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="284" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="285" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="286" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="287" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="288" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="289" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="290" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="291" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="292" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="293" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="294" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="295" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="296" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="297" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="298" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="299" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="300" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="301" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="302" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="303" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="304" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="305" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="306" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="307" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="308" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="309" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="310" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="311" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="312" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="313" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="314" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="315" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="316" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="317" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="318" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="319" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="320" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="321" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="322" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="323" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="324" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="325" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="326" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="327" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="328" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="329" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="330" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="331" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="332" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="333" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="334" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="335" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="336" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="337" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="338" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="339" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="340" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="341" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="342" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="343" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="344" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="345" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="346" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="347" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="348" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="349" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="350" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="351" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="352" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="353" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="354" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="355" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="356" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="357" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="358" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="359" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="360" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="361" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="362" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="363" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="364" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="365" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="366" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="367" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="368" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="369" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="370" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="371" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="372" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="373" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="374" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="375" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="376" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="377" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="378" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="379" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="380" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="381" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="382" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="383" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="384" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="385" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="386" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="387" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="388" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="389" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="390" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="391" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="392" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="393" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="394" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="395" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="396" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="397" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="398" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="399" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="400" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="401" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="402" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="403" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="404" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="405" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="406" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="407" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="408" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="409" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="410" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="411" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="412" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="413" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="414" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="415" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="416" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="417" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="418" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="419" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="420" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="421" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="422" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="423" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="424" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="425" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="426" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="427" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="428" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="429" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="430" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="431" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="432" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="433" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="434" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="435" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="436" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="437" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="438" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="439" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="440" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="441" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="442" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="443" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="444" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="445" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="446" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="447" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="448" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="449" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="450" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="451" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="452" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="453" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="454" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="455" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="456" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="457" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="458" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="459" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="460" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="461" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="462" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="463" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="464" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="465" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="466" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="467" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="468" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="469" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="470" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="471" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="472" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="473" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="474" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="475" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="476" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="477" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="478" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="479" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="480" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="481" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="482" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="483" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="484" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="485" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="486" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="487" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="488" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="489" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="490" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="491" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="492" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="493" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="494" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="495" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="496" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="497" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="498" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="499" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="500" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="501" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="502" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="503" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="504" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="505" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="506" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="507" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="508" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="509" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="510" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="511" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="512" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="513" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="514" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="515" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="516" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="517" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="518" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="519" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="520" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="521" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="522" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="523" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="524" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="525" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="526" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="527" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="528" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="529" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="530" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="531" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="532" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="533" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="534" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="535" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="536" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="537" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="538" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="539" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="540" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="541" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="542" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="543" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="544" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="545" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="546" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="547" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="548" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="549" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="550" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="551" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="552" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="553" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="554" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="555" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="556" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="557" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="558" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="559" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="560" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="561" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="562" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="563" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="564" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="565" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="566" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="567" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="568" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="569" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="570" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="571" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="572" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="573" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="574" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="575" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="576" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="577" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="578" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="579" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="580" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="581" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="582" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="583" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="584" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="585" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="586" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="587" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="588" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="589" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="590" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="591" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="592" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="593" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="594" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="595" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="596" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="597" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="598" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="599" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="600" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="601" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="602" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="603" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="604" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="605" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="606" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="607" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="608" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="609" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="610" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="611" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="612" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="613" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="614" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="615" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="616" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="617" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="618" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="619" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="620" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="621" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="622" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="623" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="624" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="625" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="626" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="627" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="628" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="629" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="630" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="631" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="632" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="633" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="634" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="635" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="636" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="637" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="638" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="639" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="640" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="641" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="642" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="643" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="644" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="645" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="646" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="647" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="648" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="649" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="650" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="651" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="652" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="653" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="654" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="655" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="656" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="657" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="658" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="659" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="660" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="661" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="662" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="663" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="664" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="665" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="666" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="667" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="668" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="669" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="670" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="671" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="672" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="673" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="674" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="675" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="676" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="677" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="678" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="679" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="680" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="681" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="682" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="683" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="684" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="685" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="686" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="687" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="688" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="689" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="690" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="691" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="692" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="693" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="694" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="695" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="696" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="697" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="698" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="699" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="700" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="701" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="702" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="703" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="704" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="705" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="706" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="707" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="708" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="709" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="710" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="711" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="712" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="713" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="714" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="715" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="716" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="717" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="718" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="719" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="720" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="721" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="722" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="723" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="724" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="725" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="726" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="727" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="728" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="729" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="730" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="731" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="732" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="733" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="734" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="735" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="736" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="737" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="738" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="739" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="740" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="741" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="742" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="743" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="744" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="745" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="746" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="747" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="748" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="749" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="750" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="751" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="752" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="753" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="754" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="755" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="756" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="757" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="758" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="759" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="760" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="761" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="762" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="763" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="764" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="765" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="766" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="767" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="768" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="769" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="770" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="771" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="772" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="773" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="774" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="775" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="776" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="777" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="778" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="779" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="780" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="781" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="782" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="783" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="784" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="785" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="786" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="787" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="788" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="789" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="790" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="791" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="792" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="793" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="794" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="795" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="796" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="797" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="798" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="799" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="800" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="801" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="802" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="803" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="804" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="805" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="806" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="807" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="808" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="809" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="810" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="811" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="812" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="813" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="814" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="815" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="816" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="817" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="818" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="819" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="820" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="821" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="822" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="823" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="824" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="825" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="826" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="827" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="828" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="829" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="830" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="831" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="832" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="833" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="834" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="835" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="836" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="837" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="838" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="839" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="840" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="841" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="842" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="843" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="844" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="845" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="846" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="847" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="848" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="849" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="850" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="851" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="852" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="853" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="854" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="855" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="856" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="857" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="858" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="859" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="860" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="861" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="862" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="863" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="864" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="865" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="866" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="867" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="868" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="869" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="870" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="871" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="872" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="873" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="874" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="875" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="876" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="877" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="878" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="879" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="880" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="881" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="882" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="883" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="884" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="885" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="886" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="887" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="888" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="889" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="890" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="891" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="892" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="893" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="894" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="895" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="896" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="897" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="898" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="899" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="900" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="901" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="902" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="903" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="904" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="905" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="906" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="907" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="908" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="909" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="910" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="911" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="912" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="913" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="914" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="915" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="916" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="917" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="918" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="919" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="920" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="921" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="922" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="923" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="924" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="925" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="926" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="927" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="928" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="929" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="930" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="931" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="932" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="933" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="934" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="935" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="936" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="937" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="938" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="939" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="940" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="941" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="942" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="943" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="944" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="945" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="946" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="947" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="948" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="949" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="950" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="951" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="952" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="953" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="954" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="955" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="956" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="957" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="958" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="959" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="960" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="961" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="962" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="963" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="964" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="965" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="966" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="967" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="968" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="969" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="970" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="971" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="972" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="973" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="974" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="975" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="976" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="977" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="978" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="979" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="980" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="981" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="982" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="983" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="984" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="985" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="986" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="987" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="988" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="989" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="990" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="991" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="992" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="993" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="994" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="995" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="996" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="997" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="998" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="999" spans="1:38" customHeight="1" ht="15.75"/>
+    <row r="1000" spans="1:38" customHeight="1" ht="15.75"/>
   </sheetData>
-  <mergeCells count="205">
+  <mergeCells>
     <mergeCell ref="B2:G5"/>
     <mergeCell ref="H2:AE4"/>
     <mergeCell ref="AF2:AL2"/>
@@ -2912,13 +2959,9 @@
     <mergeCell ref="AG32:AI32"/>
     <mergeCell ref="AJ32:AL32"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <printOptions gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362205" footer="0.51181102362205"/>
+  <pageSetup paperSize="1" orientation="landscape" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>